--- a/data/performance_data.xlsx
+++ b/data/performance_data.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,23 +31,13 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008B0000"/>
-        <bgColor rgb="008B0000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -70,7 +60,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -441,13 +431,6 @@
   </sheetPr>
   <dimension ref="A1:E355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -467,7 +450,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>SP500</t>
+          <t>Morningstar US Market Index</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
